--- a/jogos_2025-05-14.xlsx
+++ b/jogos_2025-05-14.xlsx
@@ -643,25 +643,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -669,83 +669,83 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.55</v>
+        <v>1.86</v>
       </c>
       <c r="M2" t="n">
-        <v>2.94</v>
+        <v>3.12</v>
       </c>
       <c r="N2" t="n">
-        <v>2.58</v>
+        <v>3.84</v>
       </c>
       <c r="O2" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="R2" t="n">
         <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="T2" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="U2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V2" t="n">
         <v>1.07</v>
       </c>
       <c r="W2" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="X2" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AB2" t="n">
         <v>1.25</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['33', '83']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>['55', '90+1']</t>
+          <t>['4']</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.45</v>
+        <v>1.83</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.05</v>
+        <v>2.65</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45791.29166666666</v>
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
         <v>2</v>
       </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.86</v>
+        <v>2.55</v>
       </c>
       <c r="M3" t="n">
-        <v>3.12</v>
+        <v>2.94</v>
       </c>
       <c r="N3" t="n">
-        <v>3.84</v>
+        <v>2.58</v>
       </c>
       <c r="O3" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="P3" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="R3" t="n">
         <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="T3" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="U3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V3" t="n">
         <v>1.07</v>
       </c>
       <c r="W3" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="AB3" t="n">
         <v>1.25</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['33', '83']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['4']</t>
+          <t>['55', '90+1']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.83</v>
+        <v>1.45</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45791.29166666666</v>
@@ -1278,35 +1278,35 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.75</v>
+        <v>6.2</v>
       </c>
       <c r="M7" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="O7" t="n">
-        <v>4.75</v>
+        <v>7</v>
       </c>
       <c r="P7" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S7" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.4</v>
-      </c>
       <c r="T7" t="n">
-        <v>2.38</v>
+        <v>3.3</v>
       </c>
       <c r="U7" t="n">
-        <v>1.55</v>
+        <v>1.27</v>
       </c>
       <c r="V7" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="X7" t="n">
-        <v>4.33</v>
+        <v>2.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.67</v>
+        <v>2.63</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.45</v>
+        <v>5.5</v>
       </c>
       <c r="AB7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.44</v>
       </c>
-      <c r="AC7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['16', '47']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['24']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AI7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45791.5</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,25 +1417,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
         <v>1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="M8" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="N8" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="O8" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="S8" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="T8" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="U8" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="V8" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="W8" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="X8" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AC8" t="n">
         <v>2.15</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['11']</t>
+          <t>['45', '83']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['39', '45+2']</t>
+          <t>['90+10']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45791.5</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tataouine</t>
+          <t>EGS Gafsa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1561,7 +1561,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1572,77 +1572,77 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['45', '69', '79']</t>
+          <t>['8', '12', '17']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>['60']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,22 +1675,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Tataouine</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1701,77 +1701,77 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>6.2</v>
+        <v>1.44</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="N10" t="n">
-        <v>1.55</v>
+        <v>6.25</v>
       </c>
       <c r="O10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q10" t="n">
         <v>7</v>
       </c>
-      <c r="P10" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.11</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="T10" t="n">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="U10" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="V10" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="W10" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="X10" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>['45', '69', '79']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH10" t="n">
         <v>2.63</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.11</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,109 +1804,109 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>EGS Gafsa</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>['11']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>['39', '45+2']</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>3</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>['8', '12', '17']</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>['60']</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45791.5</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1951,7 +1951,7 @@
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.54</v>
+        <v>4.75</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="N12" t="n">
-        <v>5.8</v>
+        <v>1.62</v>
       </c>
       <c r="O12" t="n">
-        <v>2.33</v>
+        <v>4.75</v>
       </c>
       <c r="P12" t="n">
-        <v>1.71</v>
+        <v>2.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.4</v>
+        <v>2.12</v>
       </c>
       <c r="R12" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z12" t="n">
         <v>2.2</v>
       </c>
-      <c r="T12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AA12" t="n">
-        <v>4.33</v>
+        <v>2.45</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['45', '83']</t>
+          <t>['16', '47']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['90+10']</t>
+          <t>['24']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.25</v>
+        <v>1.14</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45791.5</v>
@@ -2062,16 +2062,16 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
@@ -2088,22 +2088,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N13" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="O13" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2161,10 +2161,10 @@
         <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AJ13" t="n">
-        <v>3.5</v>
+        <v>2.38</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45791.52083333334</v>
@@ -2181,26 +2181,26 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
         <v>2</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>1.62</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>1.33</v>
+        <v>5.4</v>
       </c>
       <c r="O14" t="n">
-        <v>6.57</v>
+        <v>2.2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.02</v>
+        <v>6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['60']</t>
+          <t>['-1', '-1']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['27', '76']</t>
+          <t>['-1', '-1']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AJ14" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45791.52083333334</v>
@@ -2568,119 +2568,119 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.28</v>
+        <v>8</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>2.92</v>
+        <v>1.33</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>6.57</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>2.02</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>['60']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>['27', '76']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.38</v>
+        <v>3.75</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45791.52083333334</v>
@@ -2707,19 +2707,19 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -2733,22 +2733,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.62</v>
+        <v>2.45</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
       <c r="O18" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="P18" t="n">
         <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['-1', '-1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['-1', '-1']</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AG18" t="n">
@@ -2809,7 +2809,7 @@
         <v>1.44</v>
       </c>
       <c r="AJ18" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45791.52083333334</v>
@@ -2836,22 +2836,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Kallithea</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lamia</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.29</v>
+        <v>1.96</v>
       </c>
       <c r="M19" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>9.6</v>
+        <v>3.65</v>
       </c>
       <c r="O19" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="T19" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="U19" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W19" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="X19" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="Z19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.85</v>
       </c>
-      <c r="AA19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['2', '38', '40']</t>
+          <t>['10']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['46']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.44</v>
+        <v>2</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AJ19" t="n">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45791.58333333334</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,22 +2965,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Lamia</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2991,65 +2991,65 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.1</v>
+        <v>1.29</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="N20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X20" t="n">
         <v>3.7</v>
       </c>
-      <c r="O20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.7</v>
-      </c>
       <c r="Y20" t="n">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['79']</t>
+          <t>['2', '38', '40']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.73</v>
+        <v>3.44</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.63</v>
+        <v>4.2</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45791.58333333334</v>
@@ -3084,35 +3084,35 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kallithea</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.96</v>
+        <v>1.38</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="N21" t="n">
-        <v>3.65</v>
+        <v>6.2</v>
       </c>
       <c r="O21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T21" t="n">
         <v>2.3</v>
       </c>
-      <c r="P21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="V21" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="X21" t="n">
-        <v>3.44</v>
+        <v>5</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.16</v>
+        <v>2.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="AC21" t="n">
         <v>1.77</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['10']</t>
+          <t>['11', '55', '71']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['46']</t>
+          <t>['5', '68']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AH21" t="n">
-        <v>2</v>
+        <v>2.88</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45791.58333333334</v>
@@ -3213,119 +3213,119 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P22" t="n">
         <v>2</v>
       </c>
-      <c r="I22" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.4</v>
-      </c>
       <c r="Q22" t="n">
-        <v>6.25</v>
+        <v>4.33</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="S22" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="T22" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="U22" t="n">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="W22" t="n">
-        <v>1.17</v>
+        <v>1.45</v>
       </c>
       <c r="X22" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.55</v>
+        <v>2.38</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.47</v>
+        <v>1.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['11', '55', '71']</t>
+          <t>['79']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['5', '68']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.88</v>
+        <v>1.73</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AJ22" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45791.58333333334</v>
@@ -3997,16 +3997,16 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
         <v>2</v>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.27</v>
+        <v>6.8</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="N28" t="n">
-        <v>2.95</v>
+        <v>1.44</v>
       </c>
       <c r="O28" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="P28" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T28" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3</v>
-      </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X28" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>['52', '90+9']</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>['27', '68']</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
         <v>2.75</v>
       </c>
-      <c r="U28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W28" t="n">
+      <c r="AH28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>1.3</v>
-      </c>
-      <c r="X28" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>['72']</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>['26', '79']</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.83</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45791.625</v>
@@ -4126,22 +4126,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" t="n">
         <v>1</v>
       </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.23</v>
+        <v>1.14</v>
       </c>
       <c r="M29" t="n">
-        <v>3.21</v>
+        <v>7.2</v>
       </c>
       <c r="N29" t="n">
-        <v>3.21</v>
+        <v>21</v>
       </c>
       <c r="O29" t="n">
-        <v>2.5</v>
+        <v>1.44</v>
       </c>
       <c r="P29" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>13</v>
       </c>
       <c r="R29" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S29" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="T29" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="U29" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="V29" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="X29" t="n">
-        <v>4.75</v>
+        <v>7</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD29" t="n">
         <v>1.67</v>
       </c>
-      <c r="Z29" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['89']</t>
+          <t>['18', '21', '35', '40']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['75']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.67</v>
+        <v>7</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.57</v>
+        <v>1.14</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.38</v>
+        <v>5.5</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45791.625</v>
@@ -4255,25 +4255,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G30" t="n">
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4281,22 +4281,22 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.58</v>
+        <v>2.23</v>
       </c>
       <c r="M30" t="n">
-        <v>3.79</v>
+        <v>3.21</v>
       </c>
       <c r="N30" t="n">
-        <v>5.8</v>
+        <v>3.21</v>
       </c>
       <c r="O30" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="P30" t="n">
         <v>2.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="R30" t="n">
         <v>1.25</v>
@@ -4305,59 +4305,59 @@
         <v>3.75</v>
       </c>
       <c r="T30" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X30" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI30" t="n">
         <v>1.57</v>
       </c>
-      <c r="V30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X30" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>['36']</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>['12']</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AJ30" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45791.625</v>
@@ -4384,109 +4384,109 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
         <v>1</v>
       </c>
       <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q31" t="n">
         <v>4</v>
       </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="M31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="N31" t="n">
-        <v>21</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>13</v>
-      </c>
       <c r="R31" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="S31" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="T31" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="U31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y31" t="n">
         <v>1.8</v>
       </c>
-      <c r="V31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X31" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y31" t="n">
+      <c r="Z31" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB31" t="n">
         <v>1.38</v>
       </c>
-      <c r="Z31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AC31" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['18', '21', '35', '40']</t>
+          <t>['14']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>['75']</t>
+          <t>['79']</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="AH31" t="n">
-        <v>7</v>
+        <v>1.77</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.14</v>
+        <v>1.7</v>
       </c>
       <c r="AJ31" t="n">
-        <v>5.5</v>
+        <v>2.38</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45791.625</v>
@@ -4513,16 +4513,16 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -4539,65 +4539,65 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.23</v>
+        <v>1.19</v>
       </c>
       <c r="M32" t="n">
-        <v>3.21</v>
+        <v>6.5</v>
       </c>
       <c r="N32" t="n">
-        <v>3.21</v>
+        <v>13</v>
       </c>
       <c r="O32" t="n">
-        <v>2.88</v>
+        <v>1.53</v>
       </c>
       <c r="P32" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>11</v>
       </c>
       <c r="R32" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="S32" t="n">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="T32" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="U32" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="V32" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="X32" t="n">
-        <v>3.35</v>
+        <v>5.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.92</v>
+        <v>1.29</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.82</v>
+        <v>3.4</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.35</v>
+        <v>1.95</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.3</v>
+        <v>1.79</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AD32" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['31', '67', '70']</t>
+          <t>['45+4', '69']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.35</v>
+        <v>1.02</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.6</v>
+        <v>5.75</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.73</v>
+        <v>1.17</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45791.625</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4789,7 +4789,7 @@
         <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.88</v>
+        <v>1.58</v>
       </c>
       <c r="M34" t="n">
-        <v>3.47</v>
+        <v>3.79</v>
       </c>
       <c r="N34" t="n">
-        <v>3.97</v>
+        <v>5.8</v>
       </c>
       <c r="O34" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="P34" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="T34" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="U34" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="V34" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W34" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X34" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.94</v>
+        <v>2.29</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.95</v>
+        <v>2.3</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AC34" t="n">
         <v>1.62</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['14']</t>
+          <t>['36']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>['79']</t>
+          <t>['12']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45791.625</v>
@@ -4900,109 +4900,109 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G35" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X35" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD35" t="n">
         <v>2</v>
       </c>
-      <c r="H35" t="n">
-        <v>2</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>1</v>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="M35" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="O35" t="n">
-        <v>6</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X35" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>['52', '90+9']</t>
+          <t>['31', '67', '70']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>['27', '68']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>2.75</v>
+        <v>1.35</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="AI35" t="n">
-        <v>3.4</v>
+        <v>1.73</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45791.625</v>
@@ -5029,109 +5029,109 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="n">
         <v>2</v>
       </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
       <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
         <v>1</v>
       </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.19</v>
+        <v>2.27</v>
       </c>
       <c r="M36" t="n">
-        <v>6.5</v>
+        <v>3.45</v>
       </c>
       <c r="N36" t="n">
-        <v>13</v>
+        <v>2.95</v>
       </c>
       <c r="O36" t="n">
-        <v>1.53</v>
+        <v>3.25</v>
       </c>
       <c r="P36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S36" t="n">
         <v>3</v>
       </c>
-      <c r="Q36" t="n">
-        <v>11</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S36" t="n">
-        <v>4</v>
-      </c>
       <c r="T36" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X36" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>['72']</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>['26', '79']</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI36" t="n">
         <v>2.1</v>
       </c>
-      <c r="U36" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X36" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>['45+4', '69']</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AJ36" t="n">
-        <v>5</v>
+        <v>1.83</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45791.625</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,22 +5158,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -5184,22 +5184,22 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="M37" t="n">
-        <v>3.22</v>
+        <v>3.01</v>
       </c>
       <c r="N37" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="O37" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="P37" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="R37" t="n">
         <v>1.4</v>
@@ -5208,41 +5208,41 @@
         <v>2.75</v>
       </c>
       <c r="T37" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U37" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V37" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="W37" t="n">
         <v>1.36</v>
       </c>
       <c r="X37" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.84</v>
+        <v>3.65</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AD37" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>['46']</t>
+          <t>['7', '40', '45+2', '79', '82']</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -5251,13 +5251,13 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AH37" t="n">
         <v>1.57</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AJ37" t="n">
         <v>2.25</v>
@@ -5287,25 +5287,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.21</v>
+        <v>2.61</v>
       </c>
       <c r="M38" t="n">
-        <v>3.01</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>2.99</v>
+        <v>2.3</v>
       </c>
       <c r="O38" t="n">
         <v>2.85</v>
       </c>
       <c r="P38" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="R38" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="S38" t="n">
-        <v>2.75</v>
+        <v>3.45</v>
       </c>
       <c r="T38" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="U38" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="V38" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="W38" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="X38" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="Y38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>['13', '78']</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>['19', '30', '55']</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ38" t="n">
         <v>1.95</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>['7', '40', '45+2', '79', '82']</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>2.25</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45791.64583333334</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,109 +5416,109 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X39" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD39" t="n">
         <v>2</v>
       </c>
-      <c r="H39" t="n">
-        <v>3</v>
-      </c>
-      <c r="I39" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" t="n">
-        <v>2</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="M39" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N39" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O39" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>3</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X39" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AA39" t="n">
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>['46']</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ39" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>['13', '78']</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>['19', '30', '55']</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.95</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45791.64583333334</v>
@@ -5674,25 +5674,25 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H41" t="n">
         <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="M41" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="N41" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="O41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>5</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X41" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD41" t="n">
         <v>1.95</v>
       </c>
-      <c r="P41" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X41" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AA41" t="n">
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>['17', '31']</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>['74']</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH41" t="n">
         <v>2.1</v>
       </c>
-      <c r="AB41" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>['25', '73', '75']</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>['20']</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>2.55</v>
-      </c>
       <c r="AI41" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AJ41" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45791.65625</v>
@@ -5803,25 +5803,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H42" t="n">
         <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.94</v>
+        <v>1.45</v>
       </c>
       <c r="M42" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="N42" t="n">
-        <v>3.38</v>
+        <v>5.5</v>
       </c>
       <c r="O42" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P42" t="n">
         <v>2.5</v>
       </c>
-      <c r="P42" t="n">
+      <c r="Q42" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X42" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AA42" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q42" t="n">
-        <v>4</v>
-      </c>
-      <c r="R42" t="n">
+      <c r="AB42" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>['25', '73', '75']</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>['20']</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AI42" t="n">
         <v>1.36</v>
       </c>
-      <c r="S42" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X42" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AA42" t="n">
+      <c r="AJ42" t="n">
         <v>3.2</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>['55']</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>['90+6']</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>2.4</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45791.65625</v>
@@ -5932,25 +5932,25 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -5958,83 +5958,83 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.62</v>
+        <v>1.94</v>
       </c>
       <c r="M43" t="n">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="N43" t="n">
-        <v>2.42</v>
+        <v>3.38</v>
       </c>
       <c r="O43" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="P43" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>4</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X43" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD43" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q43" t="n">
-        <v>3</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X43" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>2</v>
-      </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>['45+5', '64']</t>
+          <t>['55']</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>['3', '10']</t>
+          <t>['90+6']</t>
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AI43" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45791.65625</v>
@@ -6061,109 +6061,109 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G44" t="n">
         <v>2</v>
       </c>
       <c r="H44" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" t="n">
         <v>1</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>2</v>
       </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.41</v>
+        <v>2.62</v>
       </c>
       <c r="M44" t="n">
-        <v>4.1</v>
+        <v>3.08</v>
       </c>
       <c r="N44" t="n">
-        <v>5.9</v>
+        <v>2.42</v>
       </c>
       <c r="O44" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="P44" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Q44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R44" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="T44" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="U44" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V44" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W44" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="X44" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AD44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>['45+5', '64']</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>['3', '10']</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ44" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>['17', '31']</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>['74']</t>
-        </is>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>3</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45791.65625</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,22 +6835,22 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -6861,83 +6861,83 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.07</v>
+        <v>2.43</v>
       </c>
       <c r="M50" t="n">
-        <v>7.8</v>
+        <v>2.99</v>
       </c>
       <c r="N50" t="n">
-        <v>19</v>
+        <v>3.25</v>
       </c>
       <c r="O50" t="n">
-        <v>1.44</v>
+        <v>3.22</v>
       </c>
       <c r="P50" t="n">
-        <v>3.1</v>
+        <v>1.77</v>
       </c>
       <c r="Q50" t="n">
-        <v>15</v>
+        <v>4.44</v>
       </c>
       <c r="R50" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U50" t="n">
         <v>1.22</v>
       </c>
-      <c r="S50" t="n">
-        <v>4</v>
-      </c>
-      <c r="T50" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.67</v>
-      </c>
       <c r="V50" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W50" t="n">
-        <v>1.15</v>
+        <v>1.55</v>
       </c>
       <c r="X50" t="n">
-        <v>5.25</v>
+        <v>2.15</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.48</v>
+        <v>1.34</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.78</v>
+        <v>5</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.92</v>
+        <v>1.11</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AD50" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>['34', '80']</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG50" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH50" t="n">
         <v>1.53</v>
       </c>
-      <c r="AE50" t="inlineStr">
-        <is>
-          <t>['68', '79', '90+3']</t>
-        </is>
-      </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG50" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>5.25</v>
-      </c>
       <c r="AI50" t="n">
-        <v>1.13</v>
+        <v>1.73</v>
       </c>
       <c r="AJ50" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45791.79166666666</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,22 +7093,22 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Nacional</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -7119,65 +7119,65 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.43</v>
+        <v>2.08</v>
       </c>
       <c r="M52" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="N52" t="n">
         <v>3.25</v>
       </c>
       <c r="O52" t="n">
-        <v>3.22</v>
+        <v>2.65</v>
       </c>
       <c r="P52" t="n">
-        <v>1.77</v>
+        <v>2.08</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.44</v>
+        <v>4.1</v>
       </c>
       <c r="R52" t="n">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="S52" t="n">
-        <v>2.28</v>
+        <v>2.7</v>
       </c>
       <c r="T52" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="U52" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="V52" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W52" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="X52" t="n">
-        <v>2.15</v>
+        <v>3.15</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="AA52" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>['34', '80']</t>
+          <t>['46']</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
@@ -7186,16 +7186,16 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AJ52" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45791.79166666666</v>
@@ -7222,16 +7222,16 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Atlético Nacional</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -7248,65 +7248,65 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.08</v>
+        <v>1.07</v>
       </c>
       <c r="M53" t="n">
-        <v>3.02</v>
+        <v>7.8</v>
       </c>
       <c r="N53" t="n">
-        <v>3.25</v>
+        <v>19</v>
       </c>
       <c r="O53" t="n">
-        <v>2.65</v>
+        <v>1.44</v>
       </c>
       <c r="P53" t="n">
-        <v>2.08</v>
+        <v>3.1</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.1</v>
+        <v>15</v>
       </c>
       <c r="R53" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="S53" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="T53" t="n">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="U53" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="V53" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W53" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="X53" t="n">
-        <v>3.15</v>
+        <v>5.25</v>
       </c>
       <c r="Y53" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.67</v>
+        <v>2.48</v>
       </c>
       <c r="AA53" t="n">
-        <v>4.2</v>
+        <v>1.78</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.23</v>
+        <v>1.92</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.88</v>
+        <v>2.38</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>['46']</t>
+          <t>['68', '79', '90+3']</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
@@ -7315,16 +7315,16 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.81</v>
+        <v>5.25</v>
       </c>
       <c r="AI53" t="n">
-        <v>1.7</v>
+        <v>1.13</v>
       </c>
       <c r="AJ53" t="n">
-        <v>2.57</v>
+        <v>6</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45791.79166666666</v>
@@ -7635,61 +7635,61 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="M56" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="N56" t="n">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="O56" t="n">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="P56" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="R56" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S56" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T56" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="U56" t="n">
         <v>1.5</v>
       </c>
       <c r="V56" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W56" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="X56" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.96</v>
+        <v>2.67</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AD56" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -7702,16 +7702,16 @@
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AH56" t="n">
-        <v>2.37</v>
+        <v>2.47</v>
       </c>
       <c r="AI56" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AK56" s="3" t="n">
         <v>45791.85416666666</v>
@@ -7738,22 +7738,22 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -7764,83 +7764,83 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.93</v>
+        <v>2.2</v>
       </c>
       <c r="M57" t="n">
-        <v>3.41</v>
+        <v>3.5</v>
       </c>
       <c r="N57" t="n">
-        <v>2.06</v>
+        <v>2.63</v>
       </c>
       <c r="O57" t="n">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="P57" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="R57" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T57" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U57" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V57" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W57" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="X57" t="n">
-        <v>3.48</v>
+        <v>3.98</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.97</v>
+        <v>2.67</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AD57" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>['29']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>1.69</v>
+        <v>1.43</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="AI57" t="n">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="AJ57" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AK57" s="3" t="n">
         <v>45791.85416666666</v>
@@ -7867,22 +7867,22 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -7893,83 +7893,83 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.2</v>
+        <v>2.93</v>
       </c>
       <c r="M58" t="n">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="N58" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="O58" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P58" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S58" t="n">
+        <v>3</v>
+      </c>
+      <c r="T58" t="n">
         <v>2.63</v>
       </c>
-      <c r="O58" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P58" t="n">
+      <c r="U58" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X58" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>['29']</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>['63']</t>
+        </is>
+      </c>
+      <c r="AG58" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI58" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q58" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R58" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S58" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T58" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U58" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V58" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W58" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X58" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="Y58" t="n">
+      <c r="AJ58" t="n">
         <v>1.67</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG58" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>2.1</v>
       </c>
       <c r="AK58" s="3" t="n">
         <v>45791.85416666666</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,22 +8254,22 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H61" t="n">
         <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -8280,83 +8280,83 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.47</v>
+        <v>2</v>
       </c>
       <c r="M61" t="n">
-        <v>3.47</v>
+        <v>3.6</v>
       </c>
       <c r="N61" t="n">
-        <v>6.7</v>
+        <v>3.85</v>
       </c>
       <c r="O61" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="P61" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q61" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R61" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="S61" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="T61" t="n">
-        <v>3.5</v>
+        <v>2.55</v>
       </c>
       <c r="U61" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="V61" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="W61" t="n">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="X61" t="n">
-        <v>2.45</v>
+        <v>3.6</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AA61" t="n">
-        <v>4.8</v>
+        <v>2.88</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="AC61" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="AD61" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>['90']</t>
+          <t>['34', '63']</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>['74']</t>
+          <t>['56']</t>
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AH61" t="n">
-        <v>2.28</v>
+        <v>1.85</v>
       </c>
       <c r="AI61" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AJ61" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AK61" s="3" t="n">
         <v>45791.89583333334</v>
@@ -8383,19 +8383,19 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G62" t="n">
         <v>2</v>
       </c>
       <c r="H62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
         <v>1</v>
@@ -8409,22 +8409,22 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.96</v>
+        <v>2.54</v>
       </c>
       <c r="M62" t="n">
-        <v>3.59</v>
+        <v>3.32</v>
       </c>
       <c r="N62" t="n">
-        <v>3.02</v>
+        <v>2.35</v>
       </c>
       <c r="O62" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="P62" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="R62" t="n">
         <v>1.36</v>
@@ -8433,59 +8433,59 @@
         <v>3</v>
       </c>
       <c r="T62" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U62" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V62" t="n">
         <v>1.05</v>
       </c>
       <c r="W62" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X62" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AA62" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>['34', '63']</t>
+          <t>['45+1', '77']</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>['56']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG62" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="AI62" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AJ62" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AK62" s="3" t="n">
         <v>45791.89583333334</v>
@@ -8512,109 +8512,109 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I63" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M63" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="N63" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="O63" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P63" t="n">
         <v>2</v>
       </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L63" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M63" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N63" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O63" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P63" t="n">
+      <c r="Q63" t="n">
+        <v>5</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S63" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q63" t="n">
-        <v>7</v>
-      </c>
-      <c r="R63" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S63" t="n">
-        <v>3.25</v>
-      </c>
       <c r="T63" t="n">
-        <v>2.63</v>
+        <v>3.75</v>
       </c>
       <c r="U63" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="V63" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W63" t="n">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="X63" t="n">
-        <v>3.74</v>
+        <v>2.3</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.77</v>
+        <v>2.43</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.93</v>
+        <v>1.56</v>
       </c>
       <c r="AA63" t="n">
-        <v>3.05</v>
+        <v>4.78</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="AC63" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>['36', '45+1', '51', '81']</t>
+          <t>['42', '52', '85']</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['62', '77']</t>
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AH63" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="AI63" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AJ63" t="n">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="AK63" s="3" t="n">
         <v>45791.89583333334</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,109 +8641,109 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M64" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="N64" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O64" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P64" t="n">
         <v>2</v>
       </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="n">
-        <v>1</v>
-      </c>
-      <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L64" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="M64" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="N64" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="O64" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P64" t="n">
+      <c r="Q64" t="n">
+        <v>7</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S64" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W64" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X64" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y64" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q64" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R64" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S64" t="n">
-        <v>3</v>
-      </c>
-      <c r="T64" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U64" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V64" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W64" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X64" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>1.85</v>
-      </c>
       <c r="Z64" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AA64" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AC64" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="AD64" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>['45+1', '77']</t>
+          <t>['90']</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>1.42</v>
+        <v>1.13</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.55</v>
+        <v>2.28</v>
       </c>
       <c r="AI64" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AJ64" t="n">
-        <v>2.3</v>
+        <v>3.35</v>
       </c>
       <c r="AK64" s="3" t="n">
         <v>45791.89583333334</v>
@@ -8770,23 +8770,23 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
         <v>2</v>
       </c>
-      <c r="I65" t="n">
-        <v>1</v>
-      </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
@@ -8796,83 +8796,83 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.87</v>
+        <v>1.39</v>
       </c>
       <c r="M65" t="n">
-        <v>3.06</v>
+        <v>4.2</v>
       </c>
       <c r="N65" t="n">
-        <v>3.87</v>
+        <v>6.3</v>
       </c>
       <c r="O65" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P65" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>7</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S65" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T65" t="n">
         <v>2.63</v>
       </c>
-      <c r="P65" t="n">
+      <c r="U65" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X65" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC65" t="n">
         <v>2</v>
       </c>
-      <c r="Q65" t="n">
-        <v>5</v>
-      </c>
-      <c r="R65" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S65" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T65" t="n">
+      <c r="AD65" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>['36', '45+1', '51', '81']</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG65" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AJ65" t="n">
         <v>3.75</v>
-      </c>
-      <c r="U65" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V65" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W65" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X65" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE65" t="inlineStr">
-        <is>
-          <t>['42', '52', '85']</t>
-        </is>
-      </c>
-      <c r="AF65" t="inlineStr">
-        <is>
-          <t>['62', '77']</t>
-        </is>
-      </c>
-      <c r="AG65" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH65" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AI65" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AJ65" t="n">
-        <v>2.88</v>
       </c>
       <c r="AK65" s="3" t="n">
         <v>45791.89583333334</v>
@@ -8925,58 +8925,58 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="M66" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N66" t="n">
-        <v>3.56</v>
+        <v>2.63</v>
       </c>
       <c r="O66" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="P66" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q66" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="R66" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="S66" t="n">
         <v>3</v>
       </c>
       <c r="T66" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="U66" t="n">
         <v>1.44</v>
       </c>
       <c r="V66" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W66" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X66" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y66" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC66" t="n">
         <v>1.7</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>1.68</v>
       </c>
       <c r="AD66" t="n">
         <v>2.05</v>
@@ -8992,16 +8992,16 @@
         </is>
       </c>
       <c r="AG66" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AI66" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ66" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK66" s="3" t="n">
         <v>45791.90625</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,22 +9028,22 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -9054,83 +9054,83 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.6</v>
+        <v>1.92</v>
       </c>
       <c r="M67" t="n">
-        <v>3.98</v>
+        <v>3.75</v>
       </c>
       <c r="N67" t="n">
-        <v>2.2</v>
+        <v>3.77</v>
       </c>
       <c r="O67" t="n">
-        <v>3.12</v>
+        <v>2.7</v>
       </c>
       <c r="P67" t="n">
-        <v>2.51</v>
+        <v>2.1</v>
       </c>
       <c r="Q67" t="n">
-        <v>2.45</v>
+        <v>3.85</v>
       </c>
       <c r="R67" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="S67" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="T67" t="n">
-        <v>2.03</v>
+        <v>2.8</v>
       </c>
       <c r="U67" t="n">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W67" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="X67" t="n">
-        <v>5.3</v>
+        <v>3.1</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.44</v>
+        <v>1.93</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.74</v>
+        <v>1.75</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.93</v>
+        <v>2.7</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.74</v>
+        <v>1.47</v>
       </c>
       <c r="AC67" t="n">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="AD67" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>['5', '18', '49', '89', '90+3']</t>
+          <t>['55']</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+2']</t>
         </is>
       </c>
       <c r="AG67" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="AI67" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AJ67" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AK67" s="3" t="n">
         <v>45791.91666666666</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,22 +9157,22 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -9183,83 +9183,83 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.16</v>
+        <v>2.6</v>
       </c>
       <c r="M68" t="n">
-        <v>3.41</v>
+        <v>3.98</v>
       </c>
       <c r="N68" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O68" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="P68" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S68" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V68" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X68" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z68" t="n">
         <v>2.74</v>
       </c>
-      <c r="O68" t="n">
-        <v>3</v>
-      </c>
-      <c r="P68" t="n">
+      <c r="AA68" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>['5', '18', '49', '89', '90+3']</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG68" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI68" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q68" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R68" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S68" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T68" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U68" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V68" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W68" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X68" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AA68" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD68" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE68" t="inlineStr">
-        <is>
-          <t>['55']</t>
-        </is>
-      </c>
-      <c r="AF68" t="inlineStr">
-        <is>
-          <t>['90+2']</t>
-        </is>
-      </c>
-      <c r="AG68" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH68" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI68" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AJ68" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AK68" s="3" t="n">
         <v>45791.91666666666</v>
@@ -9312,62 +9312,62 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="M69" t="n">
-        <v>3.6</v>
+        <v>3.41</v>
       </c>
       <c r="N69" t="n">
-        <v>3</v>
+        <v>3.23</v>
       </c>
       <c r="O69" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="P69" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.62</v>
+        <v>3.75</v>
       </c>
       <c r="R69" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S69" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T69" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="U69" t="n">
         <v>1.5</v>
       </c>
       <c r="V69" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W69" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X69" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="Z69" t="n">
         <v>2.1</v>
       </c>
       <c r="AA69" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD69" t="n">
         <v>2.25</v>
       </c>
-      <c r="AB69" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC69" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AD69" t="n">
-        <v>2.74</v>
-      </c>
       <c r="AE69" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9379,16 +9379,16 @@
         </is>
       </c>
       <c r="AG69" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AI69" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK69" s="3" t="n">
         <v>45791.9375</v>
@@ -9544,109 +9544,109 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G71" t="n">
+        <v>3</v>
+      </c>
+      <c r="H71" t="n">
+        <v>3</v>
+      </c>
+      <c r="I71" t="n">
+        <v>3</v>
+      </c>
+      <c r="J71" t="n">
         <v>2</v>
       </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" t="n">
-        <v>0</v>
-      </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.54</v>
+        <v>2.65</v>
       </c>
       <c r="M71" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="N71" t="n">
-        <v>4.35</v>
+        <v>2.22</v>
       </c>
       <c r="O71" t="n">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="P71" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="Q71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R71" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S71" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="T71" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="U71" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="V71" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W71" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="X71" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Z71" t="n">
         <v>2.1</v>
       </c>
       <c r="AA71" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AB71" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC71" t="n">
         <v>1.44</v>
       </c>
-      <c r="AC71" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AD71" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>['33', '58']</t>
+          <t>['3', '37', '45+4']</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1', '44', '52']</t>
         </is>
       </c>
       <c r="AG71" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AH71" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="AI71" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK71" s="3" t="n">
         <v>45791.97916666666</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,22 +9673,22 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -9699,65 +9699,65 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="M72" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N72" t="n">
-        <v>3.55</v>
+        <v>2.6</v>
       </c>
       <c r="O72" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="P72" t="n">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="Q72" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="R72" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="S72" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="T72" t="n">
-        <v>2.75</v>
+        <v>1.87</v>
       </c>
       <c r="U72" t="n">
-        <v>1.49</v>
+        <v>1.77</v>
       </c>
       <c r="V72" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W72" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="X72" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="Z72" t="n">
-        <v>2.1</v>
+        <v>2.85</v>
       </c>
       <c r="AA72" t="n">
-        <v>3.2</v>
+        <v>1.85</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.42</v>
+        <v>1.83</v>
       </c>
       <c r="AC72" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="AD72" t="n">
-        <v>1.9</v>
+        <v>2.98</v>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>['26', '51', '80', '86']</t>
+          <t>['13', '34', '70']</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
@@ -9766,16 +9766,16 @@
         </is>
       </c>
       <c r="AG72" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AH72" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ72" t="n">
         <v>2</v>
-      </c>
-      <c r="AI72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ72" t="n">
-        <v>0</v>
       </c>
       <c r="AK72" s="3" t="n">
         <v>45791.97916666666</v>
@@ -9802,25 +9802,25 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -9828,77 +9828,77 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="M73" t="n">
-        <v>3.5</v>
+        <v>3.69</v>
       </c>
       <c r="N73" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="O73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U73" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="V73" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W73" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X73" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="Z73" t="n">
         <v>2.1</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AC73" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AD73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>['3', '37', '45+4']</t>
+          <t>['33', '58']</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>['1', '44', '52']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG73" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH73" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,109 +9931,109 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M74" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N74" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O74" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P74" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S74" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V74" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W74" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X74" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>['26', '51', '80', '86']</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG74" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH74" t="n">
         <v>2</v>
       </c>
-      <c r="J74" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L74" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="M74" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N74" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O74" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P74" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R74" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S74" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T74" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U74" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="V74" t="n">
-        <v>0</v>
-      </c>
-      <c r="W74" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X74" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="Y74" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z74" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA74" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB74" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC74" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD74" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AE74" t="inlineStr">
-        <is>
-          <t>['13', '34', '70']</t>
-        </is>
-      </c>
-      <c r="AF74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG74" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH74" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AI74" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
         <v>45791.97916666666</v>
